--- a/output/laminas_provinciales/prov_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:06</t>
+    <t xml:space="preserve">2026-09-09 22:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:02</t>
+    <t xml:space="preserve">2026-09-17 13:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1243,18 +1243,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1295152.12</v>
+        <v>1233714.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1189921.5</v>
+        <v>1295152.12</v>
       </c>
     </row>
     <row r="4">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1233714.5</v>
+        <v>1189921.5</v>
       </c>
     </row>
   </sheetData>
@@ -1327,101 +1327,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1069051.75</v>
+        <v>1024937.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1191589.88</v>
+        <v>1155245</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1262107.5</v>
+        <v>1233714.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1070166.12</v>
+        <v>1069051.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1218693.5</v>
+        <v>1191589.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1295152.12</v>
+        <v>1262107.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>987235.12</v>
+        <v>1070166.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1112123.88</v>
+        <v>1218693.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1189921.5</v>
+        <v>1295152.12</v>
       </c>
     </row>
     <row r="11">
@@ -1558,35 +1558,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1024937.75</v>
+        <v>987235.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1155245</v>
+        <v>1112123.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1233714.5</v>
+        <v>1189921.5</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:34</t>
+    <t xml:space="preserve">2026-09-25 21:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -608,7 +608,7 @@
         <v>889058.38</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>70954.18</v>
+        <v>70954.19</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>7.98</v>
@@ -631,7 +631,7 @@
         <v>1081476.38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>81830.74</v>
+        <v>81830.75</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>7.57</v>
@@ -677,7 +677,7 @@
         <v>936351.38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>64297.24</v>
+        <v>64297.25</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>6.87</v>
@@ -723,7 +723,7 @@
         <v>1026937.75</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>71946.37</v>
+        <v>71946.38</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>7.01</v>
@@ -815,7 +815,7 @@
         <v>974410.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>71085.13</v>
+        <v>71085.12</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>7.3</v>
@@ -838,7 +838,7 @@
         <v>1222494.12</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>82271.13</v>
+        <v>82271.12</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>6.73</v>
@@ -953,7 +953,7 @@
         <v>1040462.12</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>75683.63</v>
+        <v>75683.62</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>7.27</v>
@@ -976,7 +976,7 @@
         <v>1247474.62</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>81226.76</v>
+        <v>81226.75</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>6.51</v>
@@ -1022,7 +1022,7 @@
         <v>1166270.38</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>73051.87</v>
+        <v>73051.88</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>6.26</v>
@@ -1091,7 +1091,7 @@
         <v>974676.38</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>68368.37</v>
+        <v>68368.38</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>7.01</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:33</t>
+    <t xml:space="preserve">2026-10-05 07:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -546,7 +546,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1233714</v>
+        <v>1233715</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>1155245</v>
